--- a/augmentation_log.xlsx
+++ b/augmentation_log.xlsx
@@ -471,7 +471,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -487,14 +487,14 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -503,14 +503,14 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -535,14 +535,14 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -551,14 +551,14 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -631,14 +631,14 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -647,14 +647,14 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -702,7 +702,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -711,14 +711,14 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -759,14 +759,14 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -791,14 +791,14 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -807,14 +807,14 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -839,14 +839,14 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -855,14 +855,14 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -942,7 +942,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1031,14 +1031,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1063,14 +1063,14 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1079,14 +1079,14 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1111,7 +1111,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1159,14 +1159,14 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1191,14 +1191,14 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
         <v>2</v>
@@ -1239,14 +1239,14 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
         <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1255,14 +1255,14 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1271,14 +1271,14 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1303,14 +1303,14 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1319,14 +1319,14 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1335,14 +1335,14 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1415,14 +1415,14 @@
         <v>60</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
         <v>2</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1463,14 +1463,14 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1495,14 +1495,14 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1511,14 +1511,14 @@
         <v>66</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -1543,14 +1543,14 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1559,14 +1559,14 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
@@ -1591,14 +1591,14 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1607,14 +1607,14 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
         <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1639,14 +1639,14 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1655,14 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
@@ -1687,14 +1687,14 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1703,14 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
         <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1719,14 +1719,14 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
@@ -1751,7 +1751,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
@@ -1767,14 +1767,14 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1815,14 +1815,14 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -1847,14 +1847,14 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
@@ -1879,14 +1879,14 @@
         <v>89</v>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="n">
         <v>2</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1895,14 +1895,14 @@
         <v>90</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
         <v>2</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1911,14 +1911,14 @@
         <v>91</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>

--- a/augmentation_log.xlsx
+++ b/augmentation_log.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,14 +455,14 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -487,14 +487,14 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -535,14 +535,14 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -599,14 +599,14 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -631,14 +631,14 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -663,14 +663,14 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -679,14 +679,14 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -711,14 +711,14 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -759,14 +759,14 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -775,14 +775,14 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -791,7 +791,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -823,7 +823,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -839,14 +839,14 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -855,14 +855,14 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -871,14 +871,14 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -887,14 +887,14 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -903,14 +903,14 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -919,14 +919,14 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -935,14 +935,14 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -951,14 +951,14 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -967,14 +967,14 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1015,14 +1015,14 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1031,14 +1031,14 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1047,14 +1047,14 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1063,14 +1063,14 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1079,14 +1079,14 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1095,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1127,14 +1127,14 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1143,14 +1143,14 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1191,10 +1191,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1207,14 +1207,14 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1223,14 +1223,14 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
         <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
         <v>2</v>
@@ -1271,14 +1271,14 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1303,14 +1303,14 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
@@ -1335,14 +1335,14 @@
         <v>55</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
         <v>2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1367,14 +1367,14 @@
         <v>57</v>
       </c>
       <c r="B59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
         <v>2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1383,14 +1383,14 @@
         <v>58</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1399,14 +1399,14 @@
         <v>59</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
         <v>2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
         <v>2</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1463,14 +1463,14 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1479,14 @@
         <v>64</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1543,14 @@
         <v>68</v>
       </c>
       <c r="B70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C70" t="n">
         <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1559,14 +1559,14 @@
         <v>69</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
         <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1575,14 +1575,14 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>physics</t>
         </is>
       </c>
     </row>
@@ -1591,14 +1591,14 @@
         <v>71</v>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1607,14 +1607,14 @@
         <v>72</v>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C74" t="n">
         <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1623,14 +1623,14 @@
         <v>73</v>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
         <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1639,14 +1639,14 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1655,14 @@
         <v>75</v>
       </c>
       <c r="B77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1687,14 +1687,14 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C79" t="n">
         <v>2</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1703,14 @@
         <v>78</v>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C80" t="n">
         <v>2</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>dtw</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1719,14 +1719,14 @@
         <v>79</v>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" t="n">
         <v>2</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1735,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C82" t="n">
         <v>2</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>physics</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1767,14 +1767,14 @@
         <v>82</v>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1783,14 +1783,14 @@
         <v>83</v>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
         <v>2</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>time_warp</t>
+          <t>shuffle</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
         <v>2</v>
@@ -1815,14 +1815,14 @@
         <v>85</v>
       </c>
       <c r="B87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1831,14 +1831,14 @@
         <v>86</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>time_warp</t>
         </is>
       </c>
     </row>
@@ -1847,14 +1847,14 @@
         <v>87</v>
       </c>
       <c r="B89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C89" t="n">
         <v>2</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>shuffle</t>
+          <t>dtw</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
         <v>2</v>
@@ -1890,39 +1890,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" t="n">
-        <v>3</v>
-      </c>
-      <c r="C92" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>physics</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>91</v>
-      </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" t="n">
-        <v>2</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>dtw</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>